--- a/output/generated_testcases.xlsx
+++ b/output/generated_testcases.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state!=ES_idle&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_Hwindmill_start)</t>
+          <t>!(engine_state!=ES_idle)&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_Hwindmill_start</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state!=ES_idle&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_Hwindmill_start)</t>
+          <t>engine_state!=ES_idle&amp;&amp;!(engine_state!=ES_above_idle)&amp;&amp;engine_state!=ES_Hwindmill_start</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state!=ES_idle&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_Hwindmill_start)</t>
+          <t>engine_state!=ES_idle&amp;&amp;engine_state!=ES_above_idle&amp;&amp;!(engine_state!=ES_Hwindmill_start)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;engine_state==ES_ground_start)</t>
+          <t>!(thrust_level==level_default)&amp;&amp;engine_state==ES_ground_start</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;engine_state==ES_ground_start)</t>
+          <t>thrust_level==level_default&amp;&amp;!(engine_state==ES_ground_start)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>!(thrust_level==level_default)&amp;&amp;(!(engine_state==ES_windmill_start)||engine_state==ES_Qwindmill_start||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_windmill_start)||!(engine_state==ES_Qwindmill_start)||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>!(thrust_level==level_default)&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||engine_state==ES_emergency_stop||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>!(airdis_WOW==1)&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>airdis_WOW==1&amp;&amp;!(CAS&gt;PD_ToLockCASHigh)&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;!(PLA&gt;71)&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1770,7 +1770,11 @@
           <t>PD_ToLockHLow = 0; H_TO = 24000.1; PD_ToLockCASLow = 100.1; engine_state = 0; H = 29200.1; CAS = 12000.1;</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1798,7 +1802,11 @@
           <t>PD_ToLockHLow = 18000.1; H_TO = -5999.9; airdis_WOW = true; PD_ToLockCASLow = 700.1; engine_state = 0; H = 3200.1; CAS = -23999.9;</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1826,7 +1834,11 @@
           <t>PD_ToLockHLow = 18000.1; H_TO = 6000.1; airdis_WOW = true; PD_ToLockCASLow = 900.1; engine_state = 0; H = -2000; CAS = -30000;</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1854,7 +1866,11 @@
           <t>PD_ToLockHLow = 18000.1; H_TO = 0.0999999999985448; airdis_WOW = false; PD_ToLockCASLow = 500.1; engine_state = 16; H = -1999.9; CAS = -5999.9;</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1874,7 +1890,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>!(H-H_TO&gt;PD_ToLockHLow||airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(H-H_TO&gt;PD_ToLockHLow)||!(airdis_WOW==1)&amp;&amp;CAS&lt;PD_ToLockCASLow||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -1902,7 +1918,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>!(H-H_TO&gt;PD_ToLockHLow||airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(H-H_TO&gt;PD_ToLockHLow)||!(airdis_WOW==1)&amp;&amp;CAS&lt;PD_ToLockCASLow||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1930,7 +1946,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>!(H-H_TO&gt;PD_ToLockHLow||airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(H-H_TO&gt;PD_ToLockHLow)||airdis_WOW==1&amp;&amp;!(CAS&lt;PD_ToLockCASLow)||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -1958,7 +1974,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>!(H-H_TO&gt;PD_ToLockHLow||airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(H-H_TO&gt;PD_ToLockHLow)||!(airdis_WOW==1)&amp;&amp;CAS&lt;PD_ToLockCASLow||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1994,7 +2010,11 @@
           <t>PD_ToLockHLow = 16000.1; PD_ToLockCASHigh = 0; H_TO = -30000; airdis_WOW = true; PD_ToLockCASLow = 800.1; engine_state = 16; H = 13600.1; CAS = 0.0999999999985448; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2022,7 +2042,11 @@
           <t>PD_ToLockHLow = 8000.1; PD_ToLockCASHigh = 0; H_TO = -23999.9; airdis_WOW = true; PD_ToLockCASLow = 900.1; engine_state = 16; H = 44800.1; CAS = 0.0999999999985448; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -2050,7 +2074,11 @@
           <t>PD_ToLockHLow = 0; PD_ToLockCASHigh = 400.1; H_TO = 24000.1; airdis_WOW = true; PD_ToLockCASLow = 0; engine_state = 12; H = 24000.1; CAS = 6000.1; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2078,7 +2106,11 @@
           <t>PD_ToLockHLow = 8000.1; PD_ToLockCASHigh = 0; H_TO = -23999.9; airdis_WOW = true; PD_ToLockCASLow = 900.1; engine_state = 16; H = 29200.1; CAS = 0.0999999999985448; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2106,7 +2138,11 @@
           <t>PD_ToLockHLow = 0; PD_ToLockCASHigh = 600.1; H_TO = 24000.1; airdis_WOW = true; PD_ToLockCASLow = 0.1; engine_state = 2; H = 24000.1; CAS = 6000.1; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2134,7 +2170,11 @@
           <t>PD_ToLockHLow = 10000.1; PD_ToLockCASHigh = 0; H_TO = 18000.1; airdis_WOW = true; PD_ToLockCASLow = 700.1; engine_state = 16; H = 44800.1; CAS = 0.0999999999985448; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2162,7 +2202,11 @@
           <t>PD_ToLockHLow = 0; PD_ToLockCASHigh = 0; H_TO = -23999.9; airdis_WOW = true; PD_ToLockCASLow = 600.1; engine_state = 16; H = 18800.1; CAS = 0.0999999999985448; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2190,7 +2234,11 @@
           <t>PD_ToLockHLow = 4000.1; PD_ToLockCASHigh = 0; H_TO = -5999.9; airdis_WOW = true; PD_ToLockCASLow = 700.1; engine_state = 16; H = 39600.1; CAS = 0.0999999999985448; PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>to_lock_sig=0;</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2210,7 +2258,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt))</t>
+          <t>!(!(airdis_WOW==1))&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(!(!(airdis_WOW==1))&amp;&amp;!(CAS&lt;PD_ToLockCASLow))&amp;&amp;!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2238,7 +2286,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;!(CAS&gt;PD_ToLockCASHigh)&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(H-H_TO==PD_ToLockHLow)||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2266,7 +2314,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;!(PLA&gt;71)&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;!(CAS&lt;PD_ToLockCASLow))&amp;&amp;engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2294,7 +2342,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(H-H_TO==PD_ToLockHLow)||(airdis_WOW==1&amp;&amp;!(CAS&lt;PD_ToLockCASLow))&amp;&amp;!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2322,7 +2370,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(H-H_TO==PD_ToLockHLow)||(airdis_WOW==1&amp;&amp;!(CAS&lt;PD_ToLockCASLow))&amp;&amp;engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -2350,7 +2398,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(H-H_TO==PD_ToLockHLow||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;CAS&gt;PD_ToLockCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(H-H_TO==PD_ToLockHLow)||(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)&amp;&amp;!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2538,7 +2586,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>!(airdis_WOW==1)&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2566,7 +2614,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>airdis_WOW==1&amp;&amp;!(WOW_ground_time&gt;PD_ToPhaseTime1)&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -2594,7 +2642,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;!(CAS&lt;PD_ToPhaseCASHigh)&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2622,7 +2670,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76)</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;!(PLA&gt;71)&amp;&amp;PLA&lt;=76</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -2778,7 +2826,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2806,7 +2854,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -2834,7 +2882,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2862,7 +2910,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt)</t>
+          <t>!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt)</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3178,7 +3226,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>!(airdis_WOW==1)&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||!(H-H_TO&gt;PD_ToPhaseHLow)||CAS&gt;PD_ToPhaseCASLow||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3206,7 +3254,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;!(WOW_ground_time&gt;PD_ToPhaseTime1)&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -3234,7 +3282,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;!(CAS&lt;PD_ToPhaseCASHigh)&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3262,7 +3310,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;!(PLA&gt;71)&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3290,7 +3338,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -3318,7 +3366,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3346,7 +3394,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3374,7 +3422,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(WOW_to_ground_time&gt;PD_ToPhaseTime2||H-H_TO&gt;PD_ToPhaseHLow||CAS&gt;PD_ToPhaseCASLow||engine_state==ES_flight_interrupt))</t>
+          <t>airdis_WOW==1&amp;&amp;WOW_ground_time&gt;PD_ToPhaseTime1&amp;&amp;CAS&lt;PD_ToPhaseCASHigh&amp;&amp;PLA&gt;71&amp;&amp;PLA&lt;=76&amp;&amp;(!(WOW_to_ground_time&gt;PD_ToPhaseTime2)||!(H-H_TO&gt;PD_ToPhaseHLow)||!(CAS&gt;PD_ToPhaseCASLow)||!(engine_state==ES_flight_interrupt))</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3494,7 +3542,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>!(to_lock_sig==0&amp;&amp;to_phase_sig==0)</t>
+          <t>!(to_lock_sig==0)&amp;&amp;to_phase_sig==0</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -3522,7 +3570,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>!(to_lock_sig==0&amp;&amp;to_phase_sig==0)</t>
+          <t>to_lock_sig==0&amp;&amp;!(to_phase_sig==0)</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -3642,7 +3690,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)</t>
+          <t>!(airdis_WOW==1)&amp;&amp;CAS&lt;PD_ToLockCASLow</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3670,7 +3718,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)</t>
+          <t>airdis_WOW==1&amp;&amp;!(CAS&lt;PD_ToLockCASLow)</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -3822,7 +3870,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)</t>
+          <t>!(airdis_WOW==1)&amp;&amp;CAS&lt;PD_ToLockCASLow</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -3850,7 +3898,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;CAS&lt;PD_ToLockCASLow)</t>
+          <t>airdis_WOW==1&amp;&amp;!(CAS&lt;PD_ToLockCASLow)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4770,7 +4818,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(!(N1_trim_enable==1))&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(thrust_level==level_CL)||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -4802,7 +4850,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(!(N1Trim_signal==1))&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(thrust_level==level_CR)||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -4834,7 +4882,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(!(airdis_WOW==0))&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(thrust_level==level_CL)||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(!(dPLA&lt;PD_atrimpla))))</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -4866,7 +4914,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -4898,7 +4946,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -4930,7 +4978,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -4962,7 +5010,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -4994,7 +5042,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -5026,7 +5074,7 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -5058,7 +5106,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5090,7 +5138,7 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((dspeed_state==0)||(((!(dspeed_state==1))||(!(dspeed_state==2)))&amp;&amp;(dPLA&lt;PD_atrimpla)))</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -5122,7 +5170,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(!(thrust_level==level_CT))||(!(thrust_level==level_CL))||(thrust_level==level_DCL1)||(!(thrust_level==level_DCL2)))&amp;&amp;((!(dspeed_state==0))||(((dspeed_state==1)||(!(dspeed_state==2)))&amp;&amp;(!(dPLA&lt;PD_atrimpla))))</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -5154,7 +5202,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>!((N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((thrust_level==level_MCR)||(thrust_level==level_MCT)||(thrust_level==level_MCL)||(thrust_level==level_CR)||(thrust_level==level_CT)||(thrust_level==level_CL)||(thrust_level==level_DCL1)||(thrust_level==level_DCL2))&amp;&amp;((dspeed_state==0)||(((dspeed_state==1)||(dspeed_state==2))&amp;&amp;(dPLA&lt;PD_atrimpla))))</t>
+          <t>(N1_trim_enable==1)&amp;&amp;(N1Trim_signal==1)&amp;&amp;(airdis_WOW==0)&amp;&amp;((!(thrust_level==level_MCR))||(!(thrust_level==level_MCT))||(!(thrust_level==level_MCL))||(!(thrust_level==level_CR))||(thrust_level==level_CT)||(!(thrust_level==level_CL))||(!(thrust_level==level_DCL1))||(!(thrust_level==level_DCL2)))&amp;&amp;((!(dspeed_state==0))||(((!(dspeed_state==1))||(dspeed_state==2))&amp;&amp;(!(dPLA&lt;PD_atrimpla))))</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -5250,7 +5298,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require==FLEXTO&amp;&amp;flex_dT_flag==1)</t>
+          <t>!(TL_require==FLEXTO)&amp;&amp;flex_dT_flag==1</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -5570,7 +5618,7 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(TL_require==FLEXTO&amp;&amp;flex_dT_flag==0)))</t>
+          <t>!(TL_require!=DTO1)&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(!(TL_require==FLEXTO)&amp;&amp;flex_dT_flag==0))</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -5602,7 +5650,7 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(TL_require==FLEXTO&amp;&amp;flex_dT_flag==0)))</t>
+          <t>TL_require!=DTO1&amp;&amp;!(TL_require!=DTO2)&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(!(TL_require==FLEXTO)&amp;&amp;flex_dT_flag==0))</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -5634,7 +5682,7 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(TL_require==FLEXTO&amp;&amp;flex_dT_flag==0)))</t>
+          <t>TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;!(TL_require!=GA)&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(!(TL_require==FLEXTO)&amp;&amp;flex_dT_flag==0))</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -5666,7 +5714,7 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(TL_require==FLEXTO&amp;&amp;flex_dT_flag==0)))</t>
+          <t>TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;!(TL_require!=Bump)&amp;&amp;(TL_require!=FLEXTO||(!(TL_require==FLEXTO)&amp;&amp;flex_dT_flag==0))</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
@@ -5698,7 +5746,7 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(TL_require!=FLEXTO||(TL_require==FLEXTO&amp;&amp;flex_dT_flag==0)))</t>
+          <t>TL_require!=DTO1&amp;&amp;TL_require!=DTO2&amp;&amp;TL_require!=GA&amp;&amp;TL_require!=Bump&amp;&amp;(!(TL_require!=FLEXTO)||(TL_require==FLEXTO&amp;&amp;!(flex_dT_flag==0)))</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -5794,7 +5842,7 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DCL1&amp;&amp;TL_require!=DCL2)</t>
+          <t>!(TL_require!=DCL1)&amp;&amp;TL_require!=DCL2</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
@@ -5822,7 +5870,7 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require!=DCL1&amp;&amp;TL_require!=DCL2)</t>
+          <t>TL_require!=DCL1&amp;&amp;!(TL_require!=DCL2)</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -5882,7 +5930,7 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>!(TL_require==DCL1&amp;&amp;TL_require!=DCL2)</t>
+          <t>!(TL_require==DCL1)&amp;&amp;TL_require!=DCL2</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -6006,7 +6054,7 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;PLA&lt;0)</t>
+          <t>!(airdis_WOW==1)&amp;&amp;PLA&lt;0</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -6034,7 +6082,7 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;PLA&lt;0)</t>
+          <t>airdis_WOW==1&amp;&amp;!(PLA&lt;0)</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
@@ -6126,7 +6174,7 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;PLA&gt;=0)</t>
+          <t>!(airdis_WOW==1)&amp;&amp;PLA&gt;=0</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -6154,7 +6202,7 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==1&amp;&amp;PLA&gt;=0)</t>
+          <t>airdis_WOW==1&amp;&amp;!(PLA&gt;=0)</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -6214,7 +6262,7 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==0&amp;&amp;approach_air==1)</t>
+          <t>!(airdis_WOW==0)&amp;&amp;approach_air==1</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -6242,7 +6290,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==0&amp;&amp;approach_air==1)</t>
+          <t>airdis_WOW==0&amp;&amp;!(approach_air==1)</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -6302,7 +6350,7 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==0&amp;&amp;approach_air==0)</t>
+          <t>!(airdis_WOW==0)&amp;&amp;approach_air==0</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6330,7 +6378,7 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>!(airdis_WOW==0&amp;&amp;approach_air==0)</t>
+          <t>airdis_WOW==0&amp;&amp;!(approach_air==0)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -6550,7 +6598,7 @@
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI||N2R25Dem_PLAIdle==N2R25Dem_FI||N2R25Dem_PLAIdle==N2R25Dem_AI&amp;&amp;(N1Rtr&gt;N1RDem_MCR))</t>
+          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI)||!(N2R25Dem_PLAIdle==N2R25Dem_FI)||!(N2R25Dem_PLAIdle==N2R25Dem_AI)&amp;&amp;(N1Rtr&gt;N1RDem_MCR)</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -6578,7 +6626,7 @@
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI||N2R25Dem_PLAIdle==N2R25Dem_FI||N2R25Dem_PLAIdle==N2R25Dem_AI&amp;&amp;(N1Rtr&gt;N1RDem_MCR))</t>
+          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI)||!(N2R25Dem_PLAIdle==N2R25Dem_FI)||!(N2R25Dem_PLAIdle==N2R25Dem_AI)&amp;&amp;(N1Rtr&gt;N1RDem_MCR)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
@@ -6606,7 +6654,7 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI||N2R25Dem_PLAIdle==N2R25Dem_FI||N2R25Dem_PLAIdle==N2R25Dem_AI&amp;&amp;(N1Rtr&gt;N1RDem_MCR))</t>
+          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI)||!(N2R25Dem_PLAIdle==N2R25Dem_FI)||!(N2R25Dem_PLAIdle==N2R25Dem_AI)&amp;&amp;(N1Rtr&gt;N1RDem_MCR)</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
@@ -6634,7 +6682,7 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI||N2R25Dem_PLAIdle==N2R25Dem_FI||N2R25Dem_PLAIdle==N2R25Dem_AI&amp;&amp;(N1Rtr&gt;N1RDem_MCR))</t>
+          <t>!(N2R25Dem_PLAIdle==N2R25Dem_GI)||!(N2R25Dem_PLAIdle==N2R25Dem_FI)||N2R25Dem_PLAIdle==N2R25Dem_AI&amp;&amp;(!(N1Rtr&gt;N1RDem_MCR))</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
@@ -6726,7 +6774,7 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>!(N2R25Dem_PLAIdle==N2R25Dem_RI&amp;&amp;N1Rtr&gt;N1RDem_MREV)</t>
+          <t>!(N2R25Dem_PLAIdle==N2R25Dem_RI)&amp;&amp;N1Rtr&gt;N1RDem_MREV</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -6754,7 +6802,7 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>!(N2R25Dem_PLAIdle==N2R25Dem_RI&amp;&amp;N1Rtr&gt;N1RDem_MREV)</t>
+          <t>N2R25Dem_PLAIdle==N2R25Dem_RI&amp;&amp;!(N1Rtr&gt;N1RDem_MREV)</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
@@ -6878,7 +6926,11 @@
           <t>thrust_level = 3;</t>
         </is>
       </c>
-      <c r="F213" s="3" t="inlineStr"/>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>N1RDemInd=N1RDem_BAK;</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -6906,7 +6958,11 @@
           <t>thrust_level = 5;</t>
         </is>
       </c>
-      <c r="F214" s="3" t="inlineStr"/>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>N1RDemInd=N1RDem_BAK;</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -6926,7 +6982,7 @@
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI)</t>
+          <t>!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
@@ -6954,7 +7010,7 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI)</t>
+          <t>!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -6982,7 +7038,7 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI)</t>
+          <t>!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -7010,7 +7066,7 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI)</t>
+          <t>!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
@@ -7930,7 +7986,7 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_ground_start||engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>!(thrust_level==level_default)&amp;&amp;(!(engine_state==ES_ground_start)||!(engine_state==ES_windmill_start)||engine_state==ES_Qwindmill_start||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
@@ -7958,7 +8014,7 @@
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_ground_start||engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_ground_start)||!(engine_state==ES_windmill_start)||!(engine_state==ES_Qwindmill_start)||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
@@ -7986,7 +8042,7 @@
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_ground_start||engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_ground_start)||!(engine_state==ES_windmill_start)||!(engine_state==ES_Qwindmill_start)||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
@@ -8014,7 +8070,7 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_ground_start||engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_ground_start)||!(engine_state==ES_windmill_start)||!(engine_state==ES_Qwindmill_start)||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -8042,7 +8098,7 @@
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_ground_start||engine_state==ES_windmill_start||engine_state==ES_Qwindmill_start||engine_state==ES_assist_start))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_ground_start)||!(engine_state==ES_windmill_start)||!(engine_state==ES_Qwindmill_start)||!(engine_state==ES_assist_start))</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
@@ -8358,7 +8414,7 @@
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>!(thrust_level==level_default)&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||engine_state==ES_normal_stop||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -8386,7 +8442,7 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
@@ -8414,7 +8470,7 @@
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
@@ -8442,7 +8498,7 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
@@ -8470,7 +8526,7 @@
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default&amp;&amp;(engine_state==ES_origin||engine_state==ES_ground_standby||engine_state==ES_flight_standby||engine_state==ES_cold_operation||engine_state==ES_DR_OS_Us||engine_state==ES_normal_stop||engine_state==ES_emergency_stop||engine_state==ES_ground_start_termination||engine_state==ES_flight_start_terminnation))</t>
+          <t>thrust_level==level_default&amp;&amp;(!(engine_state==ES_origin)||!(engine_state==ES_ground_standby)||!(engine_state==ES_flight_standby)||!(engine_state==ES_cold_operation)||!(engine_state==ES_DR_OS_Us)||!(engine_state==ES_normal_stop)||!(engine_state==ES_emergency_stop)||!(engine_state==ES_ground_start_termination)||!(engine_state==ES_flight_start_terminnation))</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -8506,7 +8562,11 @@
           <t>thrust_level = 0;</t>
         </is>
       </c>
-      <c r="F268" s="3" t="inlineStr"/>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>N1RDem=N1RDemInd;</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -8534,7 +8594,11 @@
           <t>thrust_level = 1;</t>
         </is>
       </c>
-      <c r="F269" s="3" t="inlineStr"/>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>N1RDem=N1RDemInd;</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -8562,7 +8626,11 @@
           <t>thrust_level = 3;</t>
         </is>
       </c>
-      <c r="F270" s="3" t="inlineStr"/>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>N1RDem=N1RDemInd;</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -8590,7 +8658,11 @@
           <t>thrust_level = 5;</t>
         </is>
       </c>
-      <c r="F271" s="3" t="inlineStr"/>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>N1RDem=N1RDemInd;</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -8618,7 +8690,11 @@
           <t>thrust_level = 7;</t>
         </is>
       </c>
-      <c r="F272" s="3" t="inlineStr"/>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>N1RDem=N1RDemInd;</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -8638,7 +8714,7 @@
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -8666,7 +8742,7 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -8694,7 +8770,7 @@
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -8722,7 +8798,7 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -8750,7 +8826,7 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -8778,7 +8854,7 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -8806,7 +8882,7 @@
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_default||thrust_level==level_MREV||thrust_level==level_REV||thrust_level==level_RI||thrust_level==level_GI||thrust_level==level_FI||thrust_level==level_AI||thrust_level==level_CR||thrust_level==level_MCR||thrust_level==level_MAX)</t>
+          <t>!(thrust_level==level_default)||!(thrust_level==level_MREV)||!(thrust_level==level_REV)||!(thrust_level==level_RI)||!(thrust_level==level_GI)||!(thrust_level==level_FI)||!(thrust_level==level_AI)||!(thrust_level==level_CR)||!(thrust_level==level_MCR)||!(thrust_level==level_MAX)</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -8834,7 +8910,7 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_MCL||thrust_level==level_DCL1||thrust_level==level_DCL2||thrust_level==level_CT||thrust_level==level_MCT||thrust_level==level_TO||thrust_level==level_MTO||thrust_level==level_DTO1||thrust_level==level_DTO2||thrust_level==level_GA||thrust_level==level_Bump||thrust_level==level_FLEXTO)</t>
+          <t>!(thrust_level==level_MCL)||!(thrust_level==level_DCL1)||!(thrust_level==level_DCL2)||!(thrust_level==level_CT)||!(thrust_level==level_MCT)||!(thrust_level==level_TO)||!(thrust_level==level_MTO)||!(thrust_level==level_DTO1)||!(thrust_level==level_DTO2)||!(thrust_level==level_GA)||!(thrust_level==level_Bump)||!(thrust_level==level_FLEXTO)</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
@@ -8862,7 +8938,7 @@
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_MCL||thrust_level==level_DCL1||thrust_level==level_DCL2||thrust_level==level_CT||thrust_level==level_MCT||thrust_level==level_TO||thrust_level==level_MTO||thrust_level==level_DTO1||thrust_level==level_DTO2||thrust_level==level_GA||thrust_level==level_Bump||thrust_level==level_FLEXTO)</t>
+          <t>!(thrust_level==level_MCL)||!(thrust_level==level_DCL1)||!(thrust_level==level_DCL2)||!(thrust_level==level_CT)||!(thrust_level==level_MCT)||!(thrust_level==level_TO)||!(thrust_level==level_MTO)||!(thrust_level==level_DTO1)||!(thrust_level==level_DTO2)||!(thrust_level==level_GA)||!(thrust_level==level_Bump)||!(thrust_level==level_FLEXTO)</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -8890,7 +8966,7 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>!(thrust_level==level_MCL||thrust_level==level_DCL1||thrust_level==level_DCL2||thrust_level==level_CT||thrust_level==level_MCT||thrust_level==level_TO||thrust_level==level_MTO||thrust_level==level_DTO1||thrust_level==level_DTO2||thrust_level==level_GA||thrust_level==level_Bump||thrust_level==level_FLEXTO)</t>
+          <t>!(thrust_level==level_MCL)||!(thrust_level==level_DCL1)||!(thrust_level==level_DCL2)||!(thrust_level==level_CT)||!(thrust_level==level_MCT)||!(thrust_level==level_TO)||!(thrust_level==level_MTO)||!(thrust_level==level_DTO1)||!(thrust_level==level_DTO2)||!(thrust_level==level_GA)||!(thrust_level==level_Bump)||!(thrust_level==level_FLEXTO)</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
@@ -9386,7 +9462,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>!(engine_state==ES_above_idle)&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -9414,7 +9490,7 @@
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
@@ -9442,7 +9518,7 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
@@ -9470,7 +9546,7 @@
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
@@ -9498,7 +9574,7 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
@@ -9526,7 +9602,7 @@
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>!(engine_state==ES_above_idle)&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((!(PLA&gt;-6-PD_IdleSwitchPlaThsld)&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr">
@@ -9554,7 +9630,7 @@
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>!(engine_state==ES_above_idle)&amp;&amp;((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
@@ -9582,7 +9658,7 @@
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>!(engine_state==ES_above_idle)&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
@@ -9610,7 +9686,7 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>!(engine_state==ES_above_idle)&amp;&amp;((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
@@ -9990,7 +10066,7 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>!(engine_state==ES_above_idle)&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||!(PLA&lt;=2)||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(!(PLA&lt;-6)||PLA&gt;2)</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
@@ -10018,7 +10094,7 @@
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||!(PLA&lt;=2)||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(!(PLA&lt;-6)||PLA&gt;2)</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -10046,7 +10122,7 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||!(PLA&lt;=2)||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(!(PLA&lt;-6)||PLA&gt;2)</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -10074,7 +10150,7 @@
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||!(PLA&lt;=2)||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(!(PLA&lt;-6)||PLA&gt;2)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -10102,7 +10178,7 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||!(PLA&lt;=2)||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(!(PLA&lt;-6)||PLA&gt;2)</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
@@ -10130,7 +10206,7 @@
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||!(PLA&gt;=-6)||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||!(PLA&gt;2))</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr">
@@ -10158,7 +10234,7 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||!(PLA&gt;=-6)||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||!(PLA&gt;2))</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -10186,7 +10262,7 @@
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||!(PLA&gt;=-6)||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||!(PLA&gt;2))</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -10214,7 +10290,7 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_above_idle&amp;&amp;(PLA&gt;=2+PD_IdleSwitchPlaThsld||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(PLA&lt;=-6-PD_IdleSwitchPlaThsld||PLA&gt;=-6||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||PLA&gt;2))</t>
+          <t>engine_state==ES_above_idle&amp;&amp;(!(PLA&gt;=2+PD_IdleSwitchPlaThsld)||PLA&lt;=2||last(PLA)&gt;2||last(PLA)&lt;0)&amp;&amp;(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||!(PLA&gt;=-6)||last(PLA)&gt;=0||last(PLA)&lt;=-6)&amp;&amp;(PLA&lt;-6||!(PLA&gt;2))</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -10338,7 +10414,7 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_Hwindmill_start&amp;&amp;thrust_level!=level_RI&amp;&amp;thrust_level!=level_GI&amp;&amp;thrust_level!=level_FI&amp;&amp;thrust_level!=level_AI)</t>
+          <t>!(engine_state==ES_Hwindmill_start)&amp;&amp;thrust_level!=level_RI&amp;&amp;thrust_level!=level_GI&amp;&amp;thrust_level!=level_FI&amp;&amp;thrust_level!=level_AI</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
@@ -10366,7 +10442,7 @@
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_Hwindmill_start&amp;&amp;thrust_level!=level_RI&amp;&amp;thrust_level!=level_GI&amp;&amp;thrust_level!=level_FI&amp;&amp;thrust_level!=level_AI)</t>
+          <t>engine_state==ES_Hwindmill_start&amp;&amp;!(thrust_level!=level_RI)&amp;&amp;thrust_level!=level_GI&amp;&amp;thrust_level!=level_FI&amp;&amp;thrust_level!=level_AI</t>
         </is>
       </c>
       <c r="E331" s="3" t="inlineStr">
@@ -10394,7 +10470,7 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state==ES_Hwindmill_start&amp;&amp;thrust_level!=level_RI&amp;&amp;thrust_level!=level_GI&amp;&amp;thrust_level!=level_FI&amp;&amp;thrust_level!=level_AI)</t>
+          <t>engine_state==ES_Hwindmill_start&amp;&amp;thrust_level!=level_RI&amp;&amp;thrust_level!=level_GI&amp;&amp;!(thrust_level!=level_FI)&amp;&amp;thrust_level!=level_AI</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
@@ -10518,7 +10594,7 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state!=ES_Hwindmill_start&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_idle)</t>
+          <t>!(engine_state!=ES_Hwindmill_start)&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_idle</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
@@ -10546,7 +10622,7 @@
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state!=ES_Hwindmill_start&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_idle)</t>
+          <t>engine_state!=ES_Hwindmill_start&amp;&amp;!(engine_state!=ES_above_idle)&amp;&amp;engine_state!=ES_idle</t>
         </is>
       </c>
       <c r="E337" s="3" t="inlineStr">
@@ -10574,7 +10650,7 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>!(engine_state!=ES_Hwindmill_start&amp;&amp;engine_state!=ES_above_idle&amp;&amp;engine_state!=ES_idle)</t>
+          <t>engine_state!=ES_Hwindmill_start&amp;&amp;engine_state!=ES_above_idle&amp;&amp;!(engine_state!=ES_idle)</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
@@ -10858,7 +10934,7 @@
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E347" s="3" t="inlineStr">
@@ -10886,7 +10962,7 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((!(PLA&gt;-6-PD_IdleSwitchPlaThsld)&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
@@ -10914,7 +10990,7 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E349" s="3" t="inlineStr">
@@ -10942,7 +11018,7 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
@@ -10970,7 +11046,7 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((!(PLA&gt;-6-PD_IdleSwitchPlaThsld)&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E351" s="3" t="inlineStr">
@@ -10998,7 +11074,7 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
@@ -11026,7 +11102,7 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E353" s="3" t="inlineStr">
@@ -11054,7 +11130,7 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
@@ -11090,7 +11166,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 25.1; PLA = 26.1;</t>
         </is>
       </c>
-      <c r="F355" s="3" t="inlineStr"/>
+      <c r="F355" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
@@ -11118,7 +11198,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 20.1; PLA = 14.3;</t>
         </is>
       </c>
-      <c r="F356" s="3" t="inlineStr"/>
+      <c r="F356" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -11146,7 +11230,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 35.1; PLA = 26.1;</t>
         </is>
       </c>
-      <c r="F357" s="3" t="inlineStr"/>
+      <c r="F357" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
@@ -11174,7 +11262,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 40.1; PLA = -33;</t>
         </is>
       </c>
-      <c r="F358" s="3" t="inlineStr"/>
+      <c r="F358" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -11202,7 +11294,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 30.1; PLA = -33;</t>
         </is>
       </c>
-      <c r="F359" s="3" t="inlineStr"/>
+      <c r="F359" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -11230,7 +11326,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 20.1; PLA = -9.3;</t>
         </is>
       </c>
-      <c r="F360" s="3" t="inlineStr"/>
+      <c r="F360" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -11258,7 +11358,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 40.1; PLA = -32.9;</t>
         </is>
       </c>
-      <c r="F361" s="3" t="inlineStr"/>
+      <c r="F361" s="3" t="inlineStr">
+        <is>
+          <t>software_control_mode=Low_Press_Control_Mode;</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -11278,7 +11382,7 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
@@ -11306,7 +11410,7 @@
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr">
@@ -11334,7 +11438,7 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
@@ -11362,7 +11466,7 @@
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E365" s="3" t="inlineStr">
@@ -11390,7 +11494,7 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((!(PLA&gt;-6-PD_IdleSwitchPlaThsld)&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
@@ -11418,7 +11522,7 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E367" s="3" t="inlineStr">
@@ -11446,7 +11550,7 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
@@ -11474,7 +11578,7 @@
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E369" s="3" t="inlineStr">
@@ -11510,7 +11614,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 40.1; PLA = 14.3;</t>
         </is>
       </c>
-      <c r="F370" s="3" t="inlineStr"/>
+      <c r="F370" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -11538,7 +11646,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 40.1; PLA = 26.1;</t>
         </is>
       </c>
-      <c r="F371" s="3" t="inlineStr"/>
+      <c r="F371" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
@@ -11566,7 +11678,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 35.1; PLA = 26.1;</t>
         </is>
       </c>
-      <c r="F372" s="3" t="inlineStr"/>
+      <c r="F372" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -11594,7 +11710,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 20.1; PLA = 2.5;</t>
         </is>
       </c>
-      <c r="F373" s="3" t="inlineStr"/>
+      <c r="F373" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
@@ -11622,7 +11742,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 35.1; PLA = -32.9;</t>
         </is>
       </c>
-      <c r="F374" s="3" t="inlineStr"/>
+      <c r="F374" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -11650,7 +11774,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 30.1; PLA = -32.9;</t>
         </is>
       </c>
-      <c r="F375" s="3" t="inlineStr"/>
+      <c r="F375" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
@@ -11678,7 +11806,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 45.1; PLA = -32.9;</t>
         </is>
       </c>
-      <c r="F376" s="3" t="inlineStr"/>
+      <c r="F376" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -11706,7 +11838,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 25.1; PLA = -21.1;</t>
         </is>
       </c>
-      <c r="F377" s="3" t="inlineStr"/>
+      <c r="F377" s="3" t="inlineStr">
+        <is>
+          <t>N1rDmd=N1Rrd;</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
@@ -11726,7 +11862,7 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
@@ -11754,7 +11890,7 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
@@ -11782,7 +11918,7 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
@@ -11810,7 +11946,7 @@
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr">
@@ -11838,7 +11974,7 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((!(PLA&gt;-6-PD_IdleSwitchPlaThsld)&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
@@ -11866,7 +12002,7 @@
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr">
@@ -11894,7 +12030,7 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
@@ -11922,7 +12058,7 @@
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr">
@@ -11958,7 +12094,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 40.1; PLA = 2.5;</t>
         </is>
       </c>
-      <c r="F386" s="3" t="inlineStr"/>
+      <c r="F386" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -11986,7 +12126,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 25.1; PLA = 26.1;</t>
         </is>
       </c>
-      <c r="F387" s="3" t="inlineStr"/>
+      <c r="F387" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -12014,7 +12158,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 30.1; PLA = 26.1;</t>
         </is>
       </c>
-      <c r="F388" s="3" t="inlineStr"/>
+      <c r="F388" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -12042,7 +12190,11 @@
           <t>last( PLA ) = 0; PD_IdleSwitchPlaThsld = 10.1; PLA = 2.5;</t>
         </is>
       </c>
-      <c r="F389" s="3" t="inlineStr"/>
+      <c r="F389" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -12070,7 +12222,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 45.1; PLA = -21.1;</t>
         </is>
       </c>
-      <c r="F390" s="3" t="inlineStr"/>
+      <c r="F390" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -12098,7 +12254,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 15.1; PLA = -9.3;</t>
         </is>
       </c>
-      <c r="F391" s="3" t="inlineStr"/>
+      <c r="F391" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
@@ -12126,7 +12286,11 @@
           <t>last( PLA ) = -1; PD_IdleSwitchPlaThsld = 10.1; PLA = -9.3;</t>
         </is>
       </c>
-      <c r="F392" s="3" t="inlineStr"/>
+      <c r="F392" s="3" t="inlineStr">
+        <is>
+          <t>N2r25Dmd=N2R25Dem;</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
@@ -12146,7 +12310,7 @@
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr">
@@ -12174,7 +12338,7 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
@@ -12202,7 +12366,7 @@
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr">
@@ -12230,7 +12394,7 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
@@ -12258,7 +12422,7 @@
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((!(PLA&gt;-6-PD_IdleSwitchPlaThsld)&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E397" s="3" t="inlineStr">
@@ -12286,7 +12450,7 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((!(PLA&lt;2+PD_IdleSwitchPlaThsld)&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&lt;-6))&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
@@ -12314,7 +12478,7 @@
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr">
@@ -12342,7 +12506,7 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>!(((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;PLA&gt;2)&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6)))</t>
+          <t>((PLA&lt;2+PD_IdleSwitchPlaThsld&amp;&amp;!(PLA&gt;2))&amp;&amp;(last(PLA)&lt;=2&amp;&amp;last(PLA)&gt;=0))||((PLA&gt;-6-PD_IdleSwitchPlaThsld&amp;&amp;PLA&lt;-6)&amp;&amp;(last(PLA)&lt;0&amp;&amp;last(PLA)&gt;-6))</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
@@ -12378,7 +12542,11 @@
           <t>PLA = 73.3;</t>
         </is>
       </c>
-      <c r="F401" s="3" t="inlineStr"/>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>N1R_1=interpolation(PS_PLA_N1Rtr_N1RDem_MCR,N1Rtr,N1RDem_MCR,PLA);N1R_2=N1RPre+N1RPre*PD_DeltN1RCo;N1Rrd=min(N1R_1,N1R_2);</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
@@ -12434,7 +12602,11 @@
           <t>PLA = -9.3;</t>
         </is>
       </c>
-      <c r="F403" s="3" t="inlineStr"/>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>N1R_1=interpolation(PS_PLA_N1Rtr_N1RDem_MREV,N1Rtr,N1RDem_MREV,PLA);N1R_2=N1RPre+N1RPre*PD_DeltN1RCo;N1Rrd=min(N1R_1,N1R_2);</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
@@ -12706,7 +12878,7 @@
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>!((abs(N1Rrd-N1Rtr)&lt;PD_N1RpIdleOut*N1RDesign)||(duration(PLA&gt;2,PD_IdleOutTime,miniSecond))||(duration(PLA&lt;-6,PD_IdleOutTime,miniSecond))||(N2R25p&gt;PD_IdleSwitchN2R25pMax)||(N1Rp&gt;PD_IdleSwitchN1RpMax)||(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||(PLA&gt;=2+PD_IdleSwitchPlaThsld)||((PLA&lt;=2)&amp;&amp;(PLA&gt;=-6))||(duration(logic_transition_mode==Logic1_Control_Mode,PD_IdleOutTime,miniSecond)))</t>
+          <t>(abs(N1Rrd-N1Rtr)&lt;PD_N1RpIdleOut*N1RDesign)||(duration(PLA&gt;2,PD_IdleOutTime,miniSecond))||(duration(PLA&lt;-6,PD_IdleOutTime,miniSecond))||(!(N2R25p&gt;PD_IdleSwitchN2R25pMax))||(!(N1Rp&gt;PD_IdleSwitchN1RpMax))||(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld))||(!(PLA&gt;=2+PD_IdleSwitchPlaThsld))||((PLA&lt;=2)&amp;&amp;(!(PLA&gt;=-6)))||(duration(logic_transition_mode==Logic1_Control_Mode,PD_IdleOutTime,miniSecond))</t>
         </is>
       </c>
       <c r="E413" s="3" t="inlineStr">
@@ -12734,7 +12906,7 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>!((abs(N1Rrd-N1Rtr)&lt;PD_N1RpIdleOut*N1RDesign)||(duration(PLA&gt;2,PD_IdleOutTime,miniSecond))||(duration(PLA&lt;-6,PD_IdleOutTime,miniSecond))||(N2R25p&gt;PD_IdleSwitchN2R25pMax)||(N1Rp&gt;PD_IdleSwitchN1RpMax)||(PLA&lt;=-6-PD_IdleSwitchPlaThsld)||(PLA&gt;=2+PD_IdleSwitchPlaThsld)||((PLA&lt;=2)&amp;&amp;(PLA&gt;=-6))||(duration(logic_transition_mode==Logic1_Control_Mode,PD_IdleOutTime,miniSecond)))</t>
+          <t>(abs(N1Rrd-N1Rtr)&lt;PD_N1RpIdleOut*N1RDesign)||(duration(PLA&gt;2,PD_IdleOutTime,miniSecond))||(duration(PLA&lt;-6,PD_IdleOutTime,miniSecond))||(!(N2R25p&gt;PD_IdleSwitchN2R25pMax))||(!(N1Rp&gt;PD_IdleSwitchN1RpMax))||(!(PLA&lt;=-6-PD_IdleSwitchPlaThsld))||(!(PLA&gt;=2+PD_IdleSwitchPlaThsld))||((!(PLA&lt;=2))&amp;&amp;(PLA&gt;=-6))||(duration(logic_transition_mode==Logic1_Control_Mode,PD_IdleOutTime,miniSecond))</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
@@ -12762,7 +12934,7 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;=2&amp;&amp;PLA&gt;=0)&amp;&amp;(last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch))</t>
+          <t>(!(PLA&lt;=2)&amp;&amp;PLA&gt;=0)&amp;&amp;(last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch)</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr">
@@ -12790,7 +12962,7 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;=2&amp;&amp;PLA&gt;=0)&amp;&amp;(last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch))</t>
+          <t>(PLA&lt;=2&amp;&amp;!(PLA&gt;=0))&amp;&amp;(last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch)</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
@@ -12818,7 +12990,7 @@
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0)&amp;&amp;(PLA&gt;=-6)&amp;&amp;(last(PLA)&gt;=-33)&amp;&amp;(last(PLA)&lt;-6)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch))</t>
+          <t>(!(PLA&lt;0))&amp;&amp;(PLA&gt;=-6)&amp;&amp;(last(PLA)&gt;=-33)&amp;&amp;(last(PLA)&lt;-6)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch)</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr">
@@ -12846,7 +13018,7 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0)&amp;&amp;(PLA&gt;=-6)&amp;&amp;(last(PLA)&gt;=-33)&amp;&amp;(last(PLA)&lt;-6)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch))</t>
+          <t>(PLA&lt;0)&amp;&amp;(!(PLA&gt;=-6))&amp;&amp;(last(PLA)&gt;=-33)&amp;&amp;(last(PLA)&lt;-6)&amp;&amp;(N2r25&lt;=N2R25Dem+N2R25Design*PD_DN2R25Switch)&amp;&amp;(N2r25&gt;=N2R25Dem-N2R25Design*PD_DN2R25Switch)</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
@@ -12874,7 +13046,7 @@
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(!(PLA&lt;0)&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||!(PLA&lt;=2)&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
@@ -12902,7 +13074,7 @@
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(PLA&lt;0&amp;&amp;!(PLA&gt;=-6)&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;!(PLA&gt;=0)&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
@@ -12930,7 +13102,7 @@
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(!(PLA&lt;0)&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||!(PLA&lt;=2)&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E421" s="3" t="inlineStr">
@@ -12958,7 +13130,7 @@
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(PLA&lt;0&amp;&amp;!(PLA&gt;=-6)&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;!(PLA&gt;=0)&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
@@ -12986,7 +13158,7 @@
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(!(PLA&lt;0)&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||!(PLA&lt;=2)&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
@@ -13014,7 +13186,7 @@
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(PLA&lt;0&amp;&amp;!(PLA&gt;=-6)&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;!(PLA&gt;=0)&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
@@ -13042,7 +13214,7 @@
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(!(PLA&lt;0)&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||!(PLA&lt;=2)&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr">
@@ -13070,7 +13242,7 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(PLA&lt;0&amp;&amp;!(PLA&gt;=-6)&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;!(PLA&gt;=0)&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
@@ -13098,7 +13270,7 @@
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(!(PLA&lt;0)&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||!(PLA&lt;=2)&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
@@ -13126,7 +13298,7 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(PLA&lt;0&amp;&amp;!(PLA&gt;=-6)&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;!(PLA&gt;=0)&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
@@ -13154,7 +13326,7 @@
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(!(PLA&lt;0)&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||!(PLA&lt;=2)&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E429" s="3" t="inlineStr">
@@ -13182,7 +13354,7 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>!((PLA&lt;0&amp;&amp;PLA&gt;=-6&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;PLA&gt;=0&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85))</t>
+          <t>(PLA&lt;0&amp;&amp;!(PLA&gt;=-6)&amp;&amp;last(PLA)&gt;=-33&amp;&amp;last(PLA)&lt;-6||PLA&lt;=2&amp;&amp;!(PLA&gt;=0)&amp;&amp;last(PLA)&gt;2&amp;&amp;last(PLA)&lt;=85)</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
@@ -13470,7 +13642,7 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>!((abs(N2R25rd-N2R25_1)&lt;N2R25Design*PD_N2R25pIdleIn1)||(duration(logic_transition_mode==Logic2_Control_Mode,PD_IdleInTime,miniSecond))||(N2r25p&lt;PD_IdleSwitchN2R25pMin)||(N1rp&lt;PD_IdleSwitchN1RpMin)||(abs(N2r25-N2R25Dem)&gt;N2R25Design*PD_N2R25pIdleIn3)||(PLA&gt;2&amp;&amp;last(PLA)&lt;=2)||(last(PLA)&gt;=-6&amp;&amp;PLA&lt;-6))</t>
+          <t>(abs(N2R25rd-N2R25_1)&lt;N2R25Design*PD_N2R25pIdleIn1)||(duration(logic_transition_mode==Logic2_Control_Mode,PD_IdleInTime,miniSecond))||(!(N2r25p&lt;PD_IdleSwitchN2R25pMin))||(!(N1rp&lt;PD_IdleSwitchN1RpMin))||(abs(N2r25-N2R25Dem)&gt;N2R25Design*PD_N2R25pIdleIn3)||(!(PLA&gt;2)&amp;&amp;last(PLA)&lt;=2)||(last(PLA)&gt;=-6&amp;&amp;PLA&lt;-6)</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
@@ -13498,7 +13670,7 @@
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>!((abs(N2R25rd-N2R25_1)&lt;N2R25Design*PD_N2R25pIdleIn1)||(duration(logic_transition_mode==Logic2_Control_Mode,PD_IdleInTime,miniSecond))||(N2r25p&lt;PD_IdleSwitchN2R25pMin)||(N1rp&lt;PD_IdleSwitchN1RpMin)||(abs(N2r25-N2R25Dem)&gt;N2R25Design*PD_N2R25pIdleIn3)||(PLA&gt;2&amp;&amp;last(PLA)&lt;=2)||(last(PLA)&gt;=-6&amp;&amp;PLA&lt;-6))</t>
+          <t>(abs(N2R25rd-N2R25_1)&lt;N2R25Design*PD_N2R25pIdleIn1)||(duration(logic_transition_mode==Logic2_Control_Mode,PD_IdleInTime,miniSecond))||(!(N2r25p&lt;PD_IdleSwitchN2R25pMin))||(!(N1rp&lt;PD_IdleSwitchN1RpMin))||(abs(N2r25-N2R25Dem)&gt;N2R25Design*PD_N2R25pIdleIn3)||(PLA&gt;2&amp;&amp;last(PLA)&lt;=2)||(last(PLA)&gt;=-6&amp;&amp;!(PLA&lt;-6))</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr">
